--- a/output/pdf_financials_xlsx/DGC.xlsx
+++ b/output/pdf_financials_xlsx/DGC.xlsx
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.056168</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.056168</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.582942</v>
       </c>
     </row>
     <row r="93">
@@ -3878,7 +3878,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4356,7 +4360,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DGC.xlsx
+++ b/output/pdf_financials_xlsx/DGC.xlsx
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.031653</v>
       </c>
     </row>
     <row r="13">
@@ -997,7 +997,7 @@
         <v>-0.096455</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.560512</v>
+        <v>-3.592165</v>
       </c>
     </row>
     <row r="28">
@@ -1039,7 +1039,7 @@
         <v>-0.096455</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.560512</v>
+        <v>-3.592165</v>
       </c>
     </row>
     <row r="30">
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001398</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.145635</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.815834</v>
       </c>
     </row>
     <row r="35">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001398</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.145635</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.815834</v>
       </c>
     </row>
     <row r="37">
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.001398</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.156135</v>
+        <v>0.0105</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.944773</v>
+        <v>0.128939</v>
       </c>
     </row>
     <row r="49">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">

--- a/output/pdf_financials_xlsx/DGC.xlsx
+++ b/output/pdf_financials_xlsx/DGC.xlsx
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0832</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.098662</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="68">
@@ -5036,7 +5036,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
